--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.456153042606422</v>
+        <v>0.2366248694235436</v>
       </c>
       <c r="D2" t="n">
-        <v>1.824926864613359</v>
+        <v>0.2965506154996708</v>
       </c>
       <c r="E2" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F2" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.867714784843464</v>
+        <v>1.441003652537063</v>
       </c>
       <c r="D3" t="n">
-        <v>8.856378207522829</v>
+        <v>1.43916145872246</v>
       </c>
       <c r="E3" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F3" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.44439688312579</v>
+        <v>3.484714493507941</v>
       </c>
       <c r="D4" t="n">
-        <v>21.20974966638723</v>
+        <v>3.446584320787925</v>
       </c>
       <c r="E4" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F4" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.23671022831511</v>
+        <v>3.125965412101206</v>
       </c>
       <c r="D5" t="n">
-        <v>19.00657780874821</v>
+        <v>3.088568893921584</v>
       </c>
       <c r="E5" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F5" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.33015097600874</v>
+        <v>5.25364953360142</v>
       </c>
       <c r="D6" t="n">
-        <v>41.182520563948</v>
+        <v>6.692159591641551</v>
       </c>
       <c r="E6" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F6" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.77972675490743</v>
+        <v>5.651705597672457</v>
       </c>
       <c r="D7" t="n">
-        <v>33.9853769543029</v>
+        <v>5.522623755074221</v>
       </c>
       <c r="E7" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F7" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.00729910962253</v>
+        <v>2.763686105313661</v>
       </c>
       <c r="D8" t="n">
-        <v>14.86597392481797</v>
+        <v>2.41572076278292</v>
       </c>
       <c r="E8" t="n">
-        <v>10.99675974856453</v>
+        <v>1.786973459141736</v>
       </c>
       <c r="F8" t="n">
-        <v>12.69132541020935</v>
+        <v>2.06234037915902</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
